--- a/BOM keyboard.xlsx
+++ b/BOM keyboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16D4E52C-6355-4A02-9776-20FE2687FD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F778C56C-8385-469C-BFF3-9A350F6FBF65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3405" yWindow="4125" windowWidth="28800" windowHeight="15345" xr2:uid="{D7B05BC2-D008-4A5C-9281-DF507E9A47A4}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>Product description</t>
   </si>
@@ -182,6 +182,12 @@
   </si>
   <si>
     <t>Used for making the keyboard sound betetr, its placed bellow the PCB</t>
+  </si>
+  <si>
+    <t>Cable for keyboard</t>
+  </si>
+  <si>
+    <t>A cool coiled cable for the cable</t>
   </si>
 </sst>
 </file>
@@ -626,7 +632,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA06CFEA-EC78-4232-85F0-5542C2F99966}">
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
@@ -716,7 +722,7 @@
         <v>1</v>
       </c>
       <c r="F4" s="3">
-        <f t="shared" ref="F4:F16" si="0">F3+D4*E4</f>
+        <f t="shared" ref="F4:F17" si="0">F3+D4*E4</f>
         <v>38.620000000000005</v>
       </c>
     </row>
@@ -970,6 +976,27 @@
       <c r="F16" s="3">
         <f t="shared" si="0"/>
         <v>146.76000000000002</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="3">
+        <v>10.77</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="0"/>
+        <v>157.53000000000003</v>
       </c>
     </row>
   </sheetData>
@@ -988,9 +1015,10 @@
     <hyperlink ref="C5" r:id="rId12" xr:uid="{0703504D-D45C-42C8-9E32-ED0AF68843BE}"/>
     <hyperlink ref="C10" r:id="rId13" xr:uid="{BF39E174-C41B-488A-AF31-01E7E585A2AE}"/>
     <hyperlink ref="C16" r:id="rId14" xr:uid="{EBE90320-2E7D-4423-B393-95086B6B09A2}"/>
+    <hyperlink ref="C17" r:id="rId15" xr:uid="{3A932C01-7F08-40B2-B6D0-80D4801F9E66}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId15"/>
-  <drawing r:id="rId16"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId16"/>
+  <drawing r:id="rId17"/>
 </worksheet>
 </file>